--- a/Revision/01_需蔡老師補做資料表/table5_subgroup_performance_with_ci.xlsx
+++ b/Revision/01_需蔡老師補做資料表/table5_subgroup_performance_with_ci.xlsx
@@ -508,43 +508,43 @@
         <v>1658</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8283852280955829</v>
+        <v>0.8513758146270818</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.828 (0.820-0.836)</t>
+          <t>0.851 (0.843-0.859)</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.8600405679513184</v>
+        <v>0.8561702127659574</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.860 (0.842-0.886)</t>
+          <t>0.856 (0.838-0.873)</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.51145958986731</v>
+        <v>0.6067551266586249</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.511 (0.488-0.534)</t>
+          <t>0.607 (0.583-0.631)</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.6414523449319214</v>
+        <v>0.710201200141193</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.641 (0.619-0.663)</t>
+          <t>0.710 (0.692-0.728)</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0.8969864713998567</v>
+        <v>0.9094239346203986</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.897 (0.889-0.905)</t>
+          <t>0.909 (0.901-0.917)</t>
         </is>
       </c>
     </row>
@@ -561,43 +561,43 @@
         <v>123</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8280346820809249</v>
+        <v>0.8251445086705202</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.828 (0.819-0.839)</t>
+          <t>0.825 (0.819-0.832)</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.625</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.625 (0.408-0.833)</t>
+          <t>0.667 (0.250-1.000)</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.08130081300813008</v>
+        <v>0.03252032520325204</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.081 (0.041-0.130)</t>
+          <t>0.033 (0.008-0.065)</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.1438848920863309</v>
+        <v>0.06201550387596899</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.144 (0.074-0.219)</t>
+          <t>0.062 (0.016-0.121)</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0.7314286939002959</v>
+        <v>0.7070384499978567</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.731 (0.682-0.774)</t>
+          <t>0.707 (0.657-0.753)</t>
         </is>
       </c>
     </row>
@@ -614,43 +614,43 @@
         <v>714</v>
       </c>
       <c r="D4" t="n">
-        <v>0.847518895826487</v>
+        <v>0.8665790338481761</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.848 (0.838-0.857)</t>
+          <t>0.867 (0.856-0.876)</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.8591954022988506</v>
+        <v>0.8362445414847162</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.859 (0.824-0.895)</t>
+          <t>0.836 (0.803-0.870)</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.4187675070028011</v>
+        <v>0.5364145658263305</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.419 (0.387-0.451)</t>
+          <t>0.536 (0.501-0.569)</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.5630885122410546</v>
+        <v>0.6535836177474402</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.563 (0.528-0.596)</t>
+          <t>0.654 (0.622-0.683)</t>
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0.8912491145019622</v>
+        <v>0.8995180725789671</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.891 (0.878-0.904)</t>
+          <t>0.900 (0.887-0.911)</t>
         </is>
       </c>
     </row>
@@ -667,43 +667,43 @@
         <v>1067</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8099590293098015</v>
+        <v>0.8310746927198235</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.810 (0.798-0.823)</t>
+          <t>0.831 (0.819-0.843)</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.8547400611620795</v>
+        <v>0.8672199170124482</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.855 (0.832-0.881)</t>
+          <t>0.867 (0.844-0.892)</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.5238987816307404</v>
+        <v>0.5876288659793815</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.524 (0.493-0.553)</t>
+          <t>0.588 (0.559-0.619)</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.6496223126089483</v>
+        <v>0.7005586592178771</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.650 (0.622-0.675)</t>
+          <t>0.701 (0.677-0.724)</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0.8786757343458373</v>
+        <v>0.8923902875792911</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.879 (0.867-0.891)</t>
+          <t>0.892 (0.881-0.905)</t>
         </is>
       </c>
     </row>
@@ -720,43 +720,43 @@
         <v>1181</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8322460391425909</v>
+        <v>0.8492544268406338</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.832 (0.823-0.841)</t>
+          <t>0.849 (0.840-0.858)</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.849772382397572</v>
+        <v>0.8485639686684073</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.850 (0.826-0.878)</t>
+          <t>0.849 (0.826-0.873)</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.4741744284504657</v>
+        <v>0.550381033022862</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.474 (0.447-0.504)</t>
+          <t>0.550 (0.520-0.576)</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.6086956521739131</v>
+        <v>0.6676938880328711</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.609 (0.583-0.636)</t>
+          <t>0.668 (0.643-0.689)</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0.8836859239469028</v>
+        <v>0.8951005840628334</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0.884 (0.874-0.894)</t>
+          <t>0.895 (0.886-0.905)</t>
         </is>
       </c>
     </row>
@@ -773,43 +773,43 @@
         <v>600</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8196465696465697</v>
+        <v>0.8466735966735967</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.820 (0.807-0.833)</t>
+          <t>0.847 (0.832-0.859)</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.8688046647230321</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.869 (0.839-0.901)</t>
+          <t>0.867 (0.839-0.898)</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.4966666666666666</v>
+        <v>0.6</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.497 (0.461-0.535)</t>
+          <t>0.600 (0.565-0.640)</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.6320254506892895</v>
+        <v>0.7093596059113301</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.632 (0.598-0.666)</t>
+          <t>0.709 (0.680-0.738)</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0.892544687814703</v>
+        <v>0.9027127391742196</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.893 (0.877-0.906)</t>
+          <t>0.903 (0.887-0.917)</t>
         </is>
       </c>
     </row>
